--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121247065</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247077</v>
+        <v>121247057</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,35 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579228</v>
+        <v>579298</v>
       </c>
       <c r="R3" t="n">
-        <v>6440768</v>
+        <v>6440736</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247021</v>
+        <v>121247151</v>
       </c>
       <c r="B4" t="n">
-        <v>91092</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +915,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579151</v>
+        <v>579124</v>
       </c>
       <c r="R4" t="n">
-        <v>6440834</v>
+        <v>6440876</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247045</v>
+        <v>121247077</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,12 +1055,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1068,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579247</v>
+        <v>579228</v>
       </c>
       <c r="R5" t="n">
-        <v>6440795</v>
+        <v>6440768</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247057</v>
+        <v>121247098</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>91102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579298</v>
+        <v>579226</v>
       </c>
       <c r="R6" t="n">
-        <v>6440736</v>
+        <v>6440747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247134</v>
+        <v>121247143</v>
       </c>
       <c r="B7" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,16 +1278,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579129</v>
+        <v>579076</v>
       </c>
       <c r="R7" t="n">
-        <v>6440893</v>
+        <v>6440858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247030</v>
+        <v>121247021</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>91102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,30 +1363,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1410,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579152</v>
+        <v>579151</v>
       </c>
       <c r="R8" t="n">
-        <v>6440848</v>
+        <v>6440834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247031</v>
+        <v>121247045</v>
       </c>
       <c r="B9" t="n">
-        <v>94844</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,38 +1481,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579146</v>
+        <v>579247</v>
       </c>
       <c r="R9" t="n">
-        <v>6440848</v>
+        <v>6440795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247098</v>
+        <v>121247030</v>
       </c>
       <c r="B10" t="n">
-        <v>91092</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,35 +1591,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1631,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579226</v>
+        <v>579152</v>
       </c>
       <c r="R10" t="n">
-        <v>6440747</v>
+        <v>6440848</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247143</v>
+        <v>121247031</v>
       </c>
       <c r="B11" t="n">
-        <v>90707</v>
+        <v>94854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,44 +1705,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579076</v>
+        <v>579146</v>
       </c>
       <c r="R11" t="n">
-        <v>6440858</v>
+        <v>6440848</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>121247034</v>
       </c>
       <c r="B12" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247121</v>
+        <v>121247134</v>
       </c>
       <c r="B13" t="n">
-        <v>91963</v>
+        <v>90717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579094</v>
+        <v>579129</v>
       </c>
       <c r="R13" t="n">
-        <v>6440903</v>
+        <v>6440893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247151</v>
+        <v>121247121</v>
       </c>
       <c r="B14" t="n">
-        <v>57501</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2040,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2080,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579124</v>
+        <v>579094</v>
       </c>
       <c r="R14" t="n">
-        <v>6440876</v>
+        <v>6440903</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,6 +2123,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247065</v>
+        <v>121247151</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579301</v>
+        <v>579124</v>
       </c>
       <c r="R2" t="n">
-        <v>6440734</v>
+        <v>6440876</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247057</v>
+        <v>121247031</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,49 +801,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579298</v>
+        <v>579146</v>
       </c>
       <c r="R3" t="n">
-        <v>6440736</v>
+        <v>6440848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247151</v>
+        <v>121247077</v>
       </c>
       <c r="B4" t="n">
         <v>57504</v>
@@ -955,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579124</v>
+        <v>579228</v>
       </c>
       <c r="R4" t="n">
-        <v>6440876</v>
+        <v>6440768</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247077</v>
+        <v>121247021</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>91102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,39 +1022,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579228</v>
+        <v>579151</v>
       </c>
       <c r="R5" t="n">
-        <v>6440768</v>
+        <v>6440834</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247098</v>
+        <v>121247030</v>
       </c>
       <c r="B6" t="n">
-        <v>91102</v>
+        <v>90717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1136,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1182,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579226</v>
+        <v>579152</v>
       </c>
       <c r="R6" t="n">
-        <v>6440747</v>
+        <v>6440848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247143</v>
+        <v>121247134</v>
       </c>
       <c r="B7" t="n">
         <v>90717</v>
@@ -1278,8 +1271,16 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1288,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579076</v>
+        <v>579129</v>
       </c>
       <c r="R7" t="n">
-        <v>6440858</v>
+        <v>6440893</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247021</v>
+        <v>121247057</v>
       </c>
       <c r="B8" t="n">
-        <v>91102</v>
+        <v>92008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1402,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579151</v>
+        <v>579298</v>
       </c>
       <c r="R8" t="n">
-        <v>6440834</v>
+        <v>6440736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247045</v>
+        <v>121247143</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>90717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,37 +1478,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1516,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579247</v>
+        <v>579076</v>
       </c>
       <c r="R9" t="n">
-        <v>6440795</v>
+        <v>6440858</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247030</v>
+        <v>121247121</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>91973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,35 +1584,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1630,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579152</v>
+        <v>579094</v>
       </c>
       <c r="R10" t="n">
-        <v>6440848</v>
+        <v>6440903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247031</v>
+        <v>121247045</v>
       </c>
       <c r="B11" t="n">
-        <v>94854</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,38 +1702,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579146</v>
+        <v>579247</v>
       </c>
       <c r="R11" t="n">
-        <v>6440848</v>
+        <v>6440795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247034</v>
+        <v>121247065</v>
       </c>
       <c r="B12" t="n">
         <v>91973</v>
@@ -1835,26 +1835,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579157</v>
+        <v>579301</v>
       </c>
       <c r="R12" t="n">
-        <v>6440837</v>
+        <v>6440734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247134</v>
+        <v>121247034</v>
       </c>
       <c r="B13" t="n">
-        <v>90717</v>
+        <v>91973</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,30 +1926,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579129</v>
+        <v>579157</v>
       </c>
       <c r="R13" t="n">
-        <v>6440893</v>
+        <v>6440837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247121</v>
+        <v>121247098</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>91102</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579094</v>
+        <v>579226</v>
       </c>
       <c r="R14" t="n">
-        <v>6440903</v>
+        <v>6440747</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247031</v>
+        <v>121247121</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,38 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579146</v>
+        <v>579094</v>
       </c>
       <c r="R3" t="n">
-        <v>6440848</v>
+        <v>6440903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247077</v>
+        <v>121247065</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,53 +915,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579228</v>
+        <v>579301</v>
       </c>
       <c r="R4" t="n">
-        <v>6440768</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247021</v>
+        <v>121247077</v>
       </c>
       <c r="B5" t="n">
-        <v>91102</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,38 +1029,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579151</v>
+        <v>579228</v>
       </c>
       <c r="R5" t="n">
-        <v>6440834</v>
+        <v>6440768</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1113,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247030</v>
+        <v>121247098</v>
       </c>
       <c r="B6" t="n">
-        <v>90717</v>
+        <v>91114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1175,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579152</v>
+        <v>579226</v>
       </c>
       <c r="R6" t="n">
-        <v>6440848</v>
+        <v>6440747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247134</v>
+        <v>121247031</v>
       </c>
       <c r="B7" t="n">
-        <v>90717</v>
+        <v>94866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,49 +1257,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579129</v>
+        <v>579146</v>
       </c>
       <c r="R7" t="n">
-        <v>6440893</v>
+        <v>6440848</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247057</v>
+        <v>121247030</v>
       </c>
       <c r="B8" t="n">
-        <v>92008</v>
+        <v>90729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,26 +1368,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579298</v>
+        <v>579152</v>
       </c>
       <c r="R8" t="n">
-        <v>6440736</v>
+        <v>6440848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247143</v>
+        <v>121247057</v>
       </c>
       <c r="B9" t="n">
-        <v>90717</v>
+        <v>92020</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,25 +1482,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1509,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579076</v>
+        <v>579298</v>
       </c>
       <c r="R9" t="n">
-        <v>6440858</v>
+        <v>6440736</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1572,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247121</v>
+        <v>121247045</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,12 +1615,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1623,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579094</v>
+        <v>579247</v>
       </c>
       <c r="R10" t="n">
-        <v>6440903</v>
+        <v>6440795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247045</v>
+        <v>121247143</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>90729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,37 +1706,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579247</v>
+        <v>579076</v>
       </c>
       <c r="R11" t="n">
-        <v>6440795</v>
+        <v>6440858</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247065</v>
+        <v>121247034</v>
       </c>
       <c r="B12" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,26 +1835,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579301</v>
+        <v>579157</v>
       </c>
       <c r="R12" t="n">
-        <v>6440734</v>
+        <v>6440837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247034</v>
+        <v>121247134</v>
       </c>
       <c r="B13" t="n">
-        <v>91973</v>
+        <v>90729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,30 +1926,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579157</v>
+        <v>579129</v>
       </c>
       <c r="R13" t="n">
-        <v>6440837</v>
+        <v>6440893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247098</v>
+        <v>121247021</v>
       </c>
       <c r="B14" t="n">
-        <v>91102</v>
+        <v>91114</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579226</v>
+        <v>579151</v>
       </c>
       <c r="R14" t="n">
-        <v>6440747</v>
+        <v>6440834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247151</v>
+        <v>121247031</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>94867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579124</v>
+        <v>579146</v>
       </c>
       <c r="R2" t="n">
-        <v>6440876</v>
+        <v>6440848</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247121</v>
+        <v>121247021</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +822,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579094</v>
+        <v>579151</v>
       </c>
       <c r="R3" t="n">
-        <v>6440903</v>
+        <v>6440834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +899,7 @@
         <v>121247065</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247077</v>
+        <v>121247143</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>90730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,35 +1026,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579228</v>
+        <v>579076</v>
       </c>
       <c r="R5" t="n">
-        <v>6440768</v>
+        <v>6440858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,6 +1097,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247098</v>
+        <v>121247045</v>
       </c>
       <c r="B6" t="n">
-        <v>91114</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,31 +1132,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1182,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579226</v>
+        <v>579247</v>
       </c>
       <c r="R6" t="n">
-        <v>6440747</v>
+        <v>6440795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247031</v>
+        <v>121247151</v>
       </c>
       <c r="B7" t="n">
-        <v>94866</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,45 +1242,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579146</v>
+        <v>579124</v>
       </c>
       <c r="R7" t="n">
-        <v>6440848</v>
+        <v>6440876</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247030</v>
+        <v>121247077</v>
       </c>
       <c r="B8" t="n">
-        <v>90729</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,12 +1382,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579152</v>
+        <v>579228</v>
       </c>
       <c r="R8" t="n">
-        <v>6440848</v>
+        <v>6440768</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247057</v>
+        <v>121247030</v>
       </c>
       <c r="B9" t="n">
-        <v>92020</v>
+        <v>90730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,26 +1474,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1517,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579298</v>
+        <v>579152</v>
       </c>
       <c r="R9" t="n">
-        <v>6440736</v>
+        <v>6440848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247045</v>
+        <v>121247057</v>
       </c>
       <c r="B10" t="n">
-        <v>91985</v>
+        <v>92021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,30 +1584,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1631,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579247</v>
+        <v>579298</v>
       </c>
       <c r="R10" t="n">
-        <v>6440795</v>
+        <v>6440736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247143</v>
+        <v>121247034</v>
       </c>
       <c r="B11" t="n">
-        <v>90729</v>
+        <v>91986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,29 +1698,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579076</v>
+        <v>579157</v>
       </c>
       <c r="R11" t="n">
-        <v>6440858</v>
+        <v>6440837</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247034</v>
+        <v>121247098</v>
       </c>
       <c r="B12" t="n">
-        <v>91985</v>
+        <v>91115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579157</v>
+        <v>579226</v>
       </c>
       <c r="R12" t="n">
-        <v>6440837</v>
+        <v>6440747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
         <v>121247134</v>
       </c>
       <c r="B13" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247021</v>
+        <v>121247121</v>
       </c>
       <c r="B14" t="n">
-        <v>91114</v>
+        <v>91986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579151</v>
+        <v>579094</v>
       </c>
       <c r="R14" t="n">
-        <v>6440834</v>
+        <v>6440903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247031</v>
+        <v>121247098</v>
       </c>
       <c r="B2" t="n">
-        <v>94867</v>
+        <v>91118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579146</v>
+        <v>579226</v>
       </c>
       <c r="R2" t="n">
-        <v>6440848</v>
+        <v>6440747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247021</v>
+        <v>121247134</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>90733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579151</v>
+        <v>579129</v>
       </c>
       <c r="R3" t="n">
-        <v>6440834</v>
+        <v>6440893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247065</v>
+        <v>121247077</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,52 +915,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579301</v>
+        <v>579228</v>
       </c>
       <c r="R4" t="n">
-        <v>6440734</v>
+        <v>6440768</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247143</v>
+        <v>121247031</v>
       </c>
       <c r="B5" t="n">
-        <v>90730</v>
+        <v>94870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,44 +1029,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579076</v>
+        <v>579146</v>
       </c>
       <c r="R5" t="n">
-        <v>6440858</v>
+        <v>6440848</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247045</v>
+        <v>121247143</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,37 +1136,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579247</v>
+        <v>579076</v>
       </c>
       <c r="R6" t="n">
-        <v>6440795</v>
+        <v>6440858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247151</v>
+        <v>121247045</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1268,13 +1268,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,13 +1281,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579124</v>
+        <v>579247</v>
       </c>
       <c r="R7" t="n">
-        <v>6440876</v>
+        <v>6440795</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247077</v>
+        <v>121247034</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>91989</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,25 +1356,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,13 +1382,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579228</v>
+        <v>579157</v>
       </c>
       <c r="R8" t="n">
-        <v>6440768</v>
+        <v>6440837</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247030</v>
+        <v>121247057</v>
       </c>
       <c r="B9" t="n">
-        <v>90730</v>
+        <v>92024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,26 +1474,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579152</v>
+        <v>579298</v>
       </c>
       <c r="R9" t="n">
-        <v>6440848</v>
+        <v>6440736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247057</v>
+        <v>121247151</v>
       </c>
       <c r="B10" t="n">
-        <v>92021</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,34 +1588,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579298</v>
+        <v>579124</v>
       </c>
       <c r="R10" t="n">
-        <v>6440736</v>
+        <v>6440876</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,7 +1668,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247034</v>
+        <v>121247121</v>
       </c>
       <c r="B11" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579157</v>
+        <v>579094</v>
       </c>
       <c r="R11" t="n">
-        <v>6440837</v>
+        <v>6440903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247098</v>
+        <v>121247021</v>
       </c>
       <c r="B12" t="n">
-        <v>91115</v>
+        <v>91118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579226</v>
+        <v>579151</v>
       </c>
       <c r="R12" t="n">
-        <v>6440747</v>
+        <v>6440834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247134</v>
+        <v>121247065</v>
       </c>
       <c r="B13" t="n">
-        <v>90730</v>
+        <v>91989</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,21 +1954,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579129</v>
+        <v>579301</v>
       </c>
       <c r="R13" t="n">
-        <v>6440893</v>
+        <v>6440734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247121</v>
+        <v>121247030</v>
       </c>
       <c r="B14" t="n">
-        <v>91986</v>
+        <v>90733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,35 +2040,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579094</v>
+        <v>579152</v>
       </c>
       <c r="R14" t="n">
-        <v>6440903</v>
+        <v>6440848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247098</v>
+        <v>121247030</v>
       </c>
       <c r="B2" t="n">
-        <v>91118</v>
+        <v>90733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579226</v>
+        <v>579152</v>
       </c>
       <c r="R2" t="n">
-        <v>6440747</v>
+        <v>6440848</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247134</v>
+        <v>121247121</v>
       </c>
       <c r="B3" t="n">
-        <v>90733</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579129</v>
+        <v>579094</v>
       </c>
       <c r="R3" t="n">
-        <v>6440893</v>
+        <v>6440903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247077</v>
+        <v>121247057</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,35 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579228</v>
+        <v>579298</v>
       </c>
       <c r="R4" t="n">
-        <v>6440768</v>
+        <v>6440736</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247031</v>
+        <v>121247143</v>
       </c>
       <c r="B5" t="n">
-        <v>94870</v>
+        <v>90733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,45 +1029,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579146</v>
+        <v>579076</v>
       </c>
       <c r="R5" t="n">
-        <v>6440848</v>
+        <v>6440858</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247143</v>
+        <v>121247098</v>
       </c>
       <c r="B6" t="n">
-        <v>90733</v>
+        <v>91118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,29 +1135,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579076</v>
+        <v>579226</v>
       </c>
       <c r="R6" t="n">
-        <v>6440858</v>
+        <v>6440747</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247045</v>
+        <v>121247034</v>
       </c>
       <c r="B7" t="n">
         <v>91989</v>
@@ -1281,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579247</v>
+        <v>579157</v>
       </c>
       <c r="R7" t="n">
-        <v>6440795</v>
+        <v>6440837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247034</v>
+        <v>121247151</v>
       </c>
       <c r="B8" t="n">
-        <v>91989</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,12 +1389,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579157</v>
+        <v>579124</v>
       </c>
       <c r="R8" t="n">
-        <v>6440837</v>
+        <v>6440876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1447,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247057</v>
+        <v>121247065</v>
       </c>
       <c r="B9" t="n">
-        <v>92024</v>
+        <v>91989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,25 +1477,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,21 +1505,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579298</v>
+        <v>579301</v>
       </c>
       <c r="R9" t="n">
-        <v>6440736</v>
+        <v>6440734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247151</v>
+        <v>121247031</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>94870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,53 +1591,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579124</v>
+        <v>579146</v>
       </c>
       <c r="R10" t="n">
-        <v>6440876</v>
+        <v>6440848</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,6 +1667,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247121</v>
+        <v>121247077</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,38 +1698,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,13 +1738,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579094</v>
+        <v>579228</v>
       </c>
       <c r="R11" t="n">
-        <v>6440903</v>
+        <v>6440768</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1782,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247021</v>
+        <v>121247045</v>
       </c>
       <c r="B12" t="n">
-        <v>91118</v>
+        <v>91989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,26 +1816,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579151</v>
+        <v>579247</v>
       </c>
       <c r="R12" t="n">
-        <v>6440834</v>
+        <v>6440795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247065</v>
+        <v>121247021</v>
       </c>
       <c r="B13" t="n">
-        <v>91989</v>
+        <v>91118</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,21 +1954,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579301</v>
+        <v>579151</v>
       </c>
       <c r="R13" t="n">
-        <v>6440734</v>
+        <v>6440834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247030</v>
+        <v>121247134</v>
       </c>
       <c r="B14" t="n">
         <v>90733</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579152</v>
+        <v>579129</v>
       </c>
       <c r="R14" t="n">
-        <v>6440848</v>
+        <v>6440893</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247030</v>
+        <v>121247034</v>
       </c>
       <c r="B2" t="n">
-        <v>90733</v>
+        <v>91995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579152</v>
+        <v>579157</v>
       </c>
       <c r="R2" t="n">
-        <v>6440848</v>
+        <v>6440837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247121</v>
+        <v>121247031</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>94876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,45 +805,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579094</v>
+        <v>579146</v>
       </c>
       <c r="R3" t="n">
-        <v>6440903</v>
+        <v>6440848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247057</v>
+        <v>121247134</v>
       </c>
       <c r="B4" t="n">
-        <v>92024</v>
+        <v>90739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579298</v>
+        <v>579129</v>
       </c>
       <c r="R4" t="n">
-        <v>6440736</v>
+        <v>6440893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247143</v>
+        <v>121247021</v>
       </c>
       <c r="B5" t="n">
-        <v>90733</v>
+        <v>91124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,29 +1022,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1060,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579076</v>
+        <v>579151</v>
       </c>
       <c r="R5" t="n">
-        <v>6440858</v>
+        <v>6440834</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247098</v>
+        <v>121247045</v>
       </c>
       <c r="B6" t="n">
-        <v>91118</v>
+        <v>91995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,31 +1140,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1174,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579226</v>
+        <v>579247</v>
       </c>
       <c r="R6" t="n">
-        <v>6440747</v>
+        <v>6440795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247034</v>
+        <v>121247098</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>91124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,31 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1288,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579157</v>
+        <v>579226</v>
       </c>
       <c r="R7" t="n">
-        <v>6440837</v>
+        <v>6440747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247151</v>
+        <v>121247121</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>91995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,39 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579124</v>
+        <v>579094</v>
       </c>
       <c r="R8" t="n">
-        <v>6440876</v>
+        <v>6440903</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,6 +1447,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247065</v>
+        <v>121247057</v>
       </c>
       <c r="B9" t="n">
-        <v>91989</v>
+        <v>92030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1505,21 +1506,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579301</v>
+        <v>579298</v>
       </c>
       <c r="R9" t="n">
-        <v>6440734</v>
+        <v>6440736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247031</v>
+        <v>121247151</v>
       </c>
       <c r="B10" t="n">
-        <v>94870</v>
+        <v>57508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,45 +1592,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579146</v>
+        <v>579124</v>
       </c>
       <c r="R10" t="n">
-        <v>6440848</v>
+        <v>6440876</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,7 +1676,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,7 +1697,7 @@
         <v>121247077</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247045</v>
+        <v>121247065</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,26 +1843,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579247</v>
+        <v>579301</v>
       </c>
       <c r="R12" t="n">
-        <v>6440795</v>
+        <v>6440734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247021</v>
+        <v>121247030</v>
       </c>
       <c r="B13" t="n">
-        <v>91118</v>
+        <v>90739</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,30 +1934,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1965,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579151</v>
+        <v>579152</v>
       </c>
       <c r="R13" t="n">
-        <v>6440834</v>
+        <v>6440848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2036,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247134</v>
+        <v>121247143</v>
       </c>
       <c r="B14" t="n">
-        <v>90733</v>
+        <v>90739</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,16 +2069,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579129</v>
+        <v>579076</v>
       </c>
       <c r="R14" t="n">
-        <v>6440893</v>
+        <v>6440858</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247065</v>
+        <v>121247030</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>90739</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,49 +1820,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579301</v>
+        <v>579152</v>
       </c>
       <c r="R12" t="n">
-        <v>6440734</v>
+        <v>6440848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247030</v>
+        <v>121247065</v>
       </c>
       <c r="B13" t="n">
-        <v>90739</v>
+        <v>91995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,49 +1934,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579152</v>
+        <v>579301</v>
       </c>
       <c r="R13" t="n">
-        <v>6440848</v>
+        <v>6440734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247034</v>
+        <v>121247021</v>
       </c>
       <c r="B2" t="n">
-        <v>91995</v>
+        <v>91125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579157</v>
+        <v>579151</v>
       </c>
       <c r="R2" t="n">
-        <v>6440837</v>
+        <v>6440834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247031</v>
+        <v>121247077</v>
       </c>
       <c r="B3" t="n">
-        <v>94876</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,45 +801,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579146</v>
+        <v>579228</v>
       </c>
       <c r="R3" t="n">
-        <v>6440848</v>
+        <v>6440768</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247134</v>
+        <v>121247121</v>
       </c>
       <c r="B4" t="n">
-        <v>90739</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,7 +943,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -947,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579129</v>
+        <v>579094</v>
       </c>
       <c r="R4" t="n">
-        <v>6440893</v>
+        <v>6440903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247021</v>
+        <v>121247045</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,26 +1033,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1061,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579151</v>
+        <v>579247</v>
       </c>
       <c r="R5" t="n">
-        <v>6440834</v>
+        <v>6440795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247045</v>
+        <v>121247031</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>94877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,45 +1147,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579247</v>
+        <v>579146</v>
       </c>
       <c r="R6" t="n">
-        <v>6440795</v>
+        <v>6440848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247098</v>
+        <v>121247057</v>
       </c>
       <c r="B7" t="n">
-        <v>91124</v>
+        <v>92031</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1250,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579226</v>
+        <v>579298</v>
       </c>
       <c r="R7" t="n">
-        <v>6440747</v>
+        <v>6440736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247121</v>
+        <v>121247151</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,38 +1364,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,13 +1404,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579094</v>
+        <v>579124</v>
       </c>
       <c r="R8" t="n">
-        <v>6440903</v>
+        <v>6440876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1448,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247057</v>
+        <v>121247098</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>91125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579298</v>
+        <v>579226</v>
       </c>
       <c r="R9" t="n">
-        <v>6440736</v>
+        <v>6440747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247151</v>
+        <v>121247030</v>
       </c>
       <c r="B10" t="n">
-        <v>57508</v>
+        <v>90740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1618,13 +1618,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,13 +1631,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579124</v>
+        <v>579152</v>
       </c>
       <c r="R10" t="n">
-        <v>6440876</v>
+        <v>6440848</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,6 +1675,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247077</v>
+        <v>121247134</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>90740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,35 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1746,13 +1745,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579228</v>
+        <v>579129</v>
       </c>
       <c r="R11" t="n">
-        <v>6440768</v>
+        <v>6440893</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,6 +1789,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247030</v>
+        <v>121247143</v>
       </c>
       <c r="B12" t="n">
-        <v>90739</v>
+        <v>90740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,16 +1841,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1859,13 +1851,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579152</v>
+        <v>579076</v>
       </c>
       <c r="R12" t="n">
-        <v>6440848</v>
+        <v>6440858</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,7 +1917,7 @@
         <v>121247065</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247143</v>
+        <v>121247034</v>
       </c>
       <c r="B14" t="n">
-        <v>90739</v>
+        <v>91996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,29 +2040,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579076</v>
+        <v>579157</v>
       </c>
       <c r="R14" t="n">
-        <v>6440858</v>
+        <v>6440837</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247021</v>
+        <v>121247045</v>
       </c>
       <c r="B2" t="n">
-        <v>91125</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579151</v>
+        <v>579247</v>
       </c>
       <c r="R2" t="n">
-        <v>6440834</v>
+        <v>6440795</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247077</v>
+        <v>121247121</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579228</v>
+        <v>579094</v>
       </c>
       <c r="R3" t="n">
-        <v>6440768</v>
+        <v>6440903</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247121</v>
+        <v>121247030</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579094</v>
+        <v>579152</v>
       </c>
       <c r="R4" t="n">
-        <v>6440903</v>
+        <v>6440848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247045</v>
+        <v>121247098</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>91125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1033,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579247</v>
+        <v>579226</v>
       </c>
       <c r="R5" t="n">
-        <v>6440795</v>
+        <v>6440747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247031</v>
+        <v>121247065</v>
       </c>
       <c r="B6" t="n">
-        <v>94877</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,27 +1147,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579146</v>
+        <v>579301</v>
       </c>
       <c r="R6" t="n">
-        <v>6440848</v>
+        <v>6440734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1352,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247151</v>
+        <v>121247034</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,13 +1397,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,13 +1410,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579124</v>
+        <v>579157</v>
       </c>
       <c r="R8" t="n">
-        <v>6440876</v>
+        <v>6440837</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,6 +1454,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247098</v>
+        <v>121247031</v>
       </c>
       <c r="B9" t="n">
-        <v>91125</v>
+        <v>94877</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,45 +1489,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579226</v>
+        <v>579146</v>
       </c>
       <c r="R9" t="n">
-        <v>6440747</v>
+        <v>6440848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247030</v>
+        <v>121247077</v>
       </c>
       <c r="B10" t="n">
-        <v>90740</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1618,12 +1618,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1631,13 +1632,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579152</v>
+        <v>579228</v>
       </c>
       <c r="R10" t="n">
-        <v>6440848</v>
+        <v>6440768</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1676,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247134</v>
+        <v>121247143</v>
       </c>
       <c r="B11" t="n">
         <v>90740</v>
@@ -1727,16 +1727,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1745,13 +1737,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579129</v>
+        <v>579076</v>
       </c>
       <c r="R11" t="n">
-        <v>6440893</v>
+        <v>6440858</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247143</v>
+        <v>121247134</v>
       </c>
       <c r="B12" t="n">
         <v>90740</v>
@@ -1841,8 +1833,16 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579076</v>
+        <v>579129</v>
       </c>
       <c r="R12" t="n">
-        <v>6440858</v>
+        <v>6440893</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247065</v>
+        <v>121247021</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>91125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,21 +1954,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579301</v>
+        <v>579151</v>
       </c>
       <c r="R13" t="n">
-        <v>6440734</v>
+        <v>6440834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247034</v>
+        <v>121247151</v>
       </c>
       <c r="B14" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2066,12 +2066,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2079,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579157</v>
+        <v>579124</v>
       </c>
       <c r="R14" t="n">
-        <v>6440837</v>
+        <v>6440876</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2123,7 +2124,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247045</v>
+        <v>121247121</v>
       </c>
       <c r="B2" t="n">
         <v>91996</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579247</v>
+        <v>579094</v>
       </c>
       <c r="R2" t="n">
-        <v>6440795</v>
+        <v>6440903</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247121</v>
+        <v>121247077</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579094</v>
+        <v>579228</v>
       </c>
       <c r="R3" t="n">
-        <v>6440903</v>
+        <v>6440768</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247030</v>
+        <v>121247143</v>
       </c>
       <c r="B4" t="n">
         <v>90740</v>
@@ -936,16 +936,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -954,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579152</v>
+        <v>579076</v>
       </c>
       <c r="R4" t="n">
-        <v>6440848</v>
+        <v>6440858</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247098</v>
+        <v>121247034</v>
       </c>
       <c r="B5" t="n">
-        <v>91125</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,31 +1025,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1068,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579226</v>
+        <v>579157</v>
       </c>
       <c r="R5" t="n">
-        <v>6440747</v>
+        <v>6440837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247065</v>
+        <v>121247134</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1171,21 +1163,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579301</v>
+        <v>579129</v>
       </c>
       <c r="R6" t="n">
-        <v>6440734</v>
+        <v>6440893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247057</v>
+        <v>121247098</v>
       </c>
       <c r="B7" t="n">
-        <v>92031</v>
+        <v>91125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1249,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1285,7 +1277,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1296,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579298</v>
+        <v>579226</v>
       </c>
       <c r="R7" t="n">
-        <v>6440736</v>
+        <v>6440747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247034</v>
+        <v>121247030</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1410,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579157</v>
+        <v>579152</v>
       </c>
       <c r="R8" t="n">
-        <v>6440837</v>
+        <v>6440848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247031</v>
+        <v>121247045</v>
       </c>
       <c r="B9" t="n">
-        <v>94877</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,38 +1481,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579146</v>
+        <v>579247</v>
       </c>
       <c r="R9" t="n">
-        <v>6440848</v>
+        <v>6440795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247077</v>
+        <v>121247021</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>91125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,39 +1591,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,13 +1630,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579228</v>
+        <v>579151</v>
       </c>
       <c r="R10" t="n">
-        <v>6440768</v>
+        <v>6440834</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,6 +1674,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247143</v>
+        <v>121247057</v>
       </c>
       <c r="B11" t="n">
-        <v>90740</v>
+        <v>92031</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1709,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1737,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579076</v>
+        <v>579298</v>
       </c>
       <c r="R11" t="n">
-        <v>6440858</v>
+        <v>6440736</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247134</v>
+        <v>121247031</v>
       </c>
       <c r="B12" t="n">
-        <v>90740</v>
+        <v>94877</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,49 +1819,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579129</v>
+        <v>579146</v>
       </c>
       <c r="R12" t="n">
-        <v>6440893</v>
+        <v>6440848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247021</v>
+        <v>121247065</v>
       </c>
       <c r="B13" t="n">
-        <v>91125</v>
+        <v>91996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,21 +1954,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579151</v>
+        <v>579301</v>
       </c>
       <c r="R13" t="n">
-        <v>6440834</v>
+        <v>6440734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247121</v>
+        <v>121247021</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>91125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579094</v>
+        <v>579151</v>
       </c>
       <c r="R2" t="n">
-        <v>6440903</v>
+        <v>6440834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247077</v>
+        <v>121247121</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579228</v>
+        <v>579094</v>
       </c>
       <c r="R3" t="n">
-        <v>6440768</v>
+        <v>6440903</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247134</v>
+        <v>121247031</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>94877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,49 +1135,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579129</v>
+        <v>579146</v>
       </c>
       <c r="R6" t="n">
-        <v>6440893</v>
+        <v>6440848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247098</v>
+        <v>121247057</v>
       </c>
       <c r="B7" t="n">
-        <v>91125</v>
+        <v>92031</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,7 +1270,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1288,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579226</v>
+        <v>579298</v>
       </c>
       <c r="R7" t="n">
-        <v>6440747</v>
+        <v>6440736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247030</v>
+        <v>121247151</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,12 +1382,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579152</v>
+        <v>579124</v>
       </c>
       <c r="R8" t="n">
-        <v>6440848</v>
+        <v>6440876</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1465,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247045</v>
+        <v>121247098</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>91125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,31 +1474,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1516,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579247</v>
+        <v>579226</v>
       </c>
       <c r="R9" t="n">
-        <v>6440795</v>
+        <v>6440747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247021</v>
+        <v>121247065</v>
       </c>
       <c r="B10" t="n">
-        <v>91125</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,21 +1588,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1619,21 +1612,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579151</v>
+        <v>579301</v>
       </c>
       <c r="R10" t="n">
-        <v>6440834</v>
+        <v>6440734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247057</v>
+        <v>121247134</v>
       </c>
       <c r="B11" t="n">
-        <v>92031</v>
+        <v>90740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,21 +1702,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1744,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579298</v>
+        <v>579129</v>
       </c>
       <c r="R11" t="n">
-        <v>6440736</v>
+        <v>6440893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247031</v>
+        <v>121247030</v>
       </c>
       <c r="B12" t="n">
-        <v>94877</v>
+        <v>90740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,39 +1812,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579146</v>
+        <v>579152</v>
       </c>
       <c r="R12" t="n">
         <v>6440848</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121247065</v>
+        <v>121247077</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,52 +1926,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579301</v>
+        <v>579228</v>
       </c>
       <c r="R13" t="n">
-        <v>6440734</v>
+        <v>6440768</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,7 +2010,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247151</v>
+        <v>121247045</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2066,13 +2066,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2080,13 +2079,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579124</v>
+        <v>579247</v>
       </c>
       <c r="R14" t="n">
-        <v>6440876</v>
+        <v>6440795</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,6 +2123,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52046-2024 artfynd.xlsx
+++ b/artfynd/A 52046-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121247021</v>
+        <v>121247031</v>
       </c>
       <c r="B2" t="n">
-        <v>91125</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579151</v>
+        <v>579146</v>
       </c>
       <c r="R2" t="n">
-        <v>6440834</v>
+        <v>6440848</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121247121</v>
+        <v>121247034</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -824,12 +807,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579094</v>
+        <v>579157</v>
       </c>
       <c r="R3" t="n">
-        <v>6440903</v>
+        <v>6440837</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121247143</v>
+        <v>121247045</v>
       </c>
       <c r="B4" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,25 +897,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -946,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579076</v>
+        <v>579247</v>
       </c>
       <c r="R4" t="n">
-        <v>6440858</v>
+        <v>6440795</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,19 +995,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121247034</v>
+        <v>121247065</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1044,26 +1025,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 52046, Fuld, Sm</t>
+          <t>A 52046, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579157</v>
+        <v>579301</v>
       </c>
       <c r="R5" t="n">
-        <v>6440837</v>
+        <v>6440734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,54 +1104,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121247031</v>
+        <v>121247121</v>
       </c>
       <c r="B6" t="n">
-        <v>94877</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579146</v>
+        <v>579094</v>
       </c>
       <c r="R6" t="n">
-        <v>6440848</v>
+        <v>6440903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,37 +1213,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121247057</v>
+        <v>121247021</v>
       </c>
       <c r="B7" t="n">
-        <v>92031</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1281,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579298</v>
+        <v>579151</v>
       </c>
       <c r="R7" t="n">
-        <v>6440736</v>
+        <v>6440834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,51 +1322,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121247151</v>
+        <v>121247098</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1368,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579124</v>
+        <v>579226</v>
       </c>
       <c r="R8" t="n">
-        <v>6440876</v>
+        <v>6440747</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1412,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,47 +1431,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121247098</v>
+        <v>121247030</v>
       </c>
       <c r="B9" t="n">
-        <v>91125</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1509,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579226</v>
+        <v>579152</v>
       </c>
       <c r="R9" t="n">
-        <v>6440747</v>
+        <v>6440848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,37 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121247065</v>
+        <v>121247134</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1612,21 +1575,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 52046, Sm</t>
+          <t>A 52046, Fuld, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579301</v>
+        <v>579129</v>
       </c>
       <c r="R10" t="n">
-        <v>6440734</v>
+        <v>6440893</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,15 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121247134</v>
+        <v>121247143</v>
       </c>
       <c r="B11" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,16 +1677,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1737,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579129</v>
+        <v>579076</v>
       </c>
       <c r="R11" t="n">
-        <v>6440893</v>
+        <v>6440858</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,15 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121247030</v>
+        <v>121247057</v>
       </c>
       <c r="B12" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,26 +1761,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1851,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579152</v>
+        <v>579298</v>
       </c>
       <c r="R12" t="n">
-        <v>6440848</v>
+        <v>6440736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,12 +1862,7 @@
         <v>121247077</v>
       </c>
       <c r="B13" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +1968,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121247045</v>
+        <v>121247151</v>
       </c>
       <c r="B14" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2066,12 +2001,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2079,13 +2015,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579247</v>
+        <v>579124</v>
       </c>
       <c r="R14" t="n">
-        <v>6440795</v>
+        <v>6440876</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2123,7 +2059,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
